--- a/www/download/COUNTRY.BEL.rpA2.xlsx
+++ b/www/download/COUNTRY.BEL.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.7299483476926</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.767200650712243</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.885559181066731</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.89852905874464</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.938262384526172</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1.08271977599631</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1.1165698681726</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.05752964628676</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.884017016719317</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.803923186934283</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.803793926163139</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.796431999331189</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.729660720440948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.679902075880751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.71694868628827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>0.729075326433899</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>0.686735810008864</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.904</t>
+          <t>0.788710055177574</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>0.787082943969255</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>0.632142960087497</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>0.586236734390419</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>0.487699934914363</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>0.370557402576921</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>0.199283907833747</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>0.0584261047579637</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.258</t>
+          <t>0.0707716766304722</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.308</t>
+          <t>0.0832848936407886</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>0.135150346281362</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>0.271980712616782</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>0.196128782685844</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>0.0952267442101364</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>0.0607780857800362</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>0.118537474609437</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.268</t>
+          <t>0.112008040067751</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>0.0219055947317714</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>-0.021075346392544</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.0845673186741445</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.165091315469403</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>-0.294332009023739</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.507</t>
+          <t>-0.350122712285771</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>-0.337652069380704</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>-0.325169545895535</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.672</t>
+          <t>-0.304038790005865</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>-0.235023522922756</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>-0.283415213555036</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>-0.524067524469179</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>-0.53773020830399</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>-0.511860199456345</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>-0.51368681335357</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>-0.559284464426745</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>-0.568150574584892</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>-0.595653794457791</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>-0.633641241688837</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>-0.736201363260347</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>-0.712768838930998</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>-0.7064269228059</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>-0.700896679914326</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>-0.675866066641681</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>-0.647930595327888</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>-0.670956422632486</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>24806295937.3893</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>23790740807.3766</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>22706357263.177</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>23203027572.9715</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>23900653321.9648</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>26163873633.7901</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>26299052340.594</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>25811121412.6758</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>27913513659.1959</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>30099377862.5618</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>29435862520.6249</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>31697299437.7597</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>33103553932.0101</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>38847240678.4863</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>30166197079.4224</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>11023736976.3116</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>11375771192.1043</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>10945338077.0258</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>11223996090.7726</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>12536141914.4075</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>13446883813.5677</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14625027038.5231</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>15977365195.8524</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>19530036472.1357</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>20891766414.335</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>20799357063.6683</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20797973738.592</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20308887126.2903</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18972370178.7166</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>19903212189.1483</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>1787719.19717339</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>1798483.9401099</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>1895410.45411337</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>1903271.66411814</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>2031396.83093024</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>2250827.46392409</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>2249843.4268863</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>2146039.34376743</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>1935759.24441848</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>1805654.23342952</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>1742439.23821827</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>1672254.80758942</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>1502139.51157822</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>1561611.34117403</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>1458048.78650936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>27568.9209984434</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>27579.081484161</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>27540.2497467636</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>27606.1819578746</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28872.177835669</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>30046.8358120284</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>29421.6076652858</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>29564.6995818328</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>31640.3931534227</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>35060.4393372264</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>37489.5890940798</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>39621.2914175593</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>45258.9284331775</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52056.5041752607</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>47481.3153358806</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>108208.767161476</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>103461.844139846</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>97118.1927747096</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>98019.2941700692</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>104170.997456941</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>114685.714599094</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>111203.865645677</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>110543.757862824</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>127995.021198717</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>149694.832079969</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>155715.045545528</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>174516.951096672</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>204319.429938507</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>261924.98753764</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>187997.271054275</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>0.0259306144199154</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>0.00923075493601355</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>51.79</t>
+          <t>0.0771083669061059</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>0.0825749535680445</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>-0.00375374774583304</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>53.78</t>
+          <t>-0.0247868685475643</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>-0.0784778064164131</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>-0.152980933788753</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>-0.303556272991232</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>55.91</t>
+          <t>-0.325876403364135</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>56.43</t>
+          <t>-0.309437778890024</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>56.91</t>
+          <t>-0.293606453520773</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>-0.259741948721863</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>-0.160621822740825</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>54.34</t>
+          <t>-0.205010426901766</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>62182.6622563998</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>61459.7852163008</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>54898.5796373611</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>57959.8632996363</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16.52</t>
+          <t>58927.178840252</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>54204.1396966795</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>56140.9223292916</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>59000.2544874741</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>73014.0204700645</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>85672.9263729353</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>90857.4369084485</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>96451.1149533829</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>109746.04455259</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>124144.43780264</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>119286.866911306</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7299483476926</t>
+          <t>3478.70252922336</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.767200650712243</t>
+          <t>3584.97619961063</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885559181066731</t>
+          <t>3422.05217898602</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89852905874464</t>
+          <t>3434.72868442337</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262384526172</t>
+          <t>3773.02113193191</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977599631</t>
+          <t>3946.72993079667</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1165698681726</t>
+          <t>4215.17409098623</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964628676</t>
+          <t>4604.56999563168</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017016719317</t>
+          <t>5625.61000801804</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923186934283</t>
+          <t>5957.06327478331</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793926163139</t>
+          <t>5836.91848987187</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999331189</t>
+          <t>5762.08944259985</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720440948</t>
+          <t>5530.11768176808</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902075880751</t>
+          <t>5075.08289881747</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694868628827</t>
+          <t>5354.80546875459</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>18105346992.2276</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>18111965722.9864</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>16864441912.7923</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>17114198515.6194</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>18737866830.2749</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>19055540579.2512</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>20083528913.6197</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>22735638336.3314</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>27161620849.3634</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>29432183954.5171</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>28909395285.1315</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>28944342633.0018</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>28888139101.0162</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>25832181250.5249</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>26155300791.8008</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>16250162729.9958</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>15797015727.8548</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>14753385083.9025</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>14936287382.5391</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>16305635447.3295</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>17364395324.8204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>17505813749.1419</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>19202548942.0581</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>24092235473.8181</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>25594516218.7438</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>25671728109.68</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>25679195583.7946</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>25276741435.9661</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>22046560044.6728</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>21884171290.2477</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1855184262.23175</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>2314949995.13161</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>2111056828.8898</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>2177911133.0802</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>2432231382.94541</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>1691145254.43078</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>2577715164.47785</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>3533089394.27332</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>3069385375.54529</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>3837667735.77337</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>3237667175.45155</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>3265147049.20722</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.477</t>
+          <t>3611397665.0501</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>3785621205.85216</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>4271129501.55314</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>3568.90742319024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>3618.06823636068</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>3685.92103397511</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>3718.35124605846</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>3758.85816236294</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>3848.90285480927</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>3884.37647466233</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>3900.15857800427</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>3917.92080068191</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>4015.79692018435</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>4030.75539680381</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.849</t>
+          <t>4070.30279648862</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>4093.71413844441</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>4259.91383304862</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>4257.0145136293</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>3526.35628582448</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>3579.39726207956</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>3652.02477145389</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>3686.8972812327</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>3735.65798346286</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>3830.72356776891</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>3876.19458747481</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>3893.34420631727</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>3922.77303018103</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>4026.45741181088</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>4047.09313071097</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>4095.39092840921</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>4114.33017739017</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>4280.9702890865</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>4296.09294655663</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>177513.724249902</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>173479.376536638</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>164690.676764728</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>78.71</t>
+          <t>162774.108847925</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>63.21</t>
+          <t>160458.565785168</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>58.62</t>
+          <t>161850.185048457</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>48.77</t>
+          <t>162421.29888976</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>170547.540206467</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>200681.067021766</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>238705.533185001</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>247065.800135292</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>273343.026589669</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>324688.835284459</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>375094.150818069</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>301037.714775515</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11613053142.459</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>11227733570.6018</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11022279555.8423</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10858017152.1489</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>11022769345.9319</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>12381482454.9411</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>12193451402.217</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>12003582101.1468</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-29.43</t>
+          <t>13302859150.8805</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-35.01</t>
+          <t>14691197621.3853</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-33.77</t>
+          <t>14820032475.7426</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-32.52</t>
+          <t>16154426938.5735</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-30.4</t>
+          <t>17198797611.6888</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-23.5</t>
+          <t>20753145757.5548</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-28.34</t>
+          <t>14791266828.9367</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-52.41</t>
+          <t>155354.044170616</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-53.77</t>
+          <t>152499.637195941</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-51.19</t>
+          <t>143810.096571035</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>144436.832500273</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-55.93</t>
+          <t>141951.659026442</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-56.82</t>
+          <t>147219.957489576</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-59.57</t>
+          <t>146747.689357156</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>148688.660044613</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-73.62</t>
+          <t>175032.757146186</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-71.28</t>
+          <t>210429.495545863</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-70.64</t>
+          <t>221153.776608734</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-70.09</t>
+          <t>246146.915333527</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-67.59</t>
+          <t>292889.792187384</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-64.79</t>
+          <t>354991.525157902</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-67.1</t>
+          <t>275136.130911899</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13637.055</t>
+          <t>23345776091.3852</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13879.478</t>
+          <t>23434755285.8486</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14258.067</t>
+          <t>22420488340.0922</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14647.151</t>
+          <t>22863378015.3537</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15045.755</t>
+          <t>24406031135.1409</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>15740.278</t>
+          <t>27111960057.2677</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16146.021</t>
+          <t>27368143605.831</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16192.208</t>
+          <t>27905235394.0002</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16320.43</t>
+          <t>32870206881.4893</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16906.052</t>
+          <t>36360849114.8129</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17232.559</t>
+          <t>37104188005.4816</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>17644.971</t>
+          <t>38708184933.6619</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>18012.982</t>
+          <t>39453118429.2888</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>19049.861</t>
+          <t>42792294656.0985</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>19064.151</t>
+          <t>35496568765.1741</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11309.589</t>
+          <t>22159.6800792858</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11480.778</t>
+          <t>20979.7393406965</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11789.315</t>
+          <t>20880.5801936927</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12150.817</t>
+          <t>18337.2763476516</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12489.084</t>
+          <t>18506.9067587257</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13113.578</t>
+          <t>14630.227558881</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13477.287</t>
+          <t>15673.6095326039</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13533.133</t>
+          <t>21858.880161855</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>13601.571</t>
+          <t>25648.3098755797</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>14083.633</t>
+          <t>28276.0376391382</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>14363.25</t>
+          <t>25912.0235265583</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>14691.554</t>
+          <t>27196.1112561413</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>15033.817</t>
+          <t>31799.0430970755</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>15924.993</t>
+          <t>20102.6256601672</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>15822.846</t>
+          <t>25901.5838636155</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24806.296</t>
+          <t>-11732722948.9263</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23790.741</t>
+          <t>-12207021715.2468</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22706.357</t>
+          <t>-11398208784.2499</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23203.028</t>
+          <t>-12005360863.2048</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23900.653</t>
+          <t>-13383261789.209</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>26163.874</t>
+          <t>-14730477602.3266</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>26299.052</t>
+          <t>-15174692203.614</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>25811.121</t>
+          <t>-15901653292.8534</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>27913.514</t>
+          <t>-19567347730.6089</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30099.378</t>
+          <t>-21669651493.4276</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>29435.863</t>
+          <t>-22284155529.7389</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>31697.299</t>
+          <t>-22553757995.0885</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>33103.554</t>
+          <t>-22254320817.6</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>38847.241</t>
+          <t>-22039148898.5437</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>30166.197</t>
+          <t>-20705301936.2374</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>117847.10491</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>112987.65254</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>102377.91139</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>103401.21995</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>100904.07742</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>91991.6699</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>90815.81233</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>97443.41446</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>118505.86321</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>135255.33413</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>137671.1065</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>145710.11847</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>166173.53261</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>183373.46257</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>168451.19134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6320.031</t>
+          <t>0.0252644913529974</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6341.727</t>
+          <t>0.0220593624470564</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6438.945</t>
+          <t>0.0239556813852598</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6534.907</t>
+          <t>0.0227886677505537</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6624.338</t>
+          <t>0.0175323313582896</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6854.747</t>
+          <t>0.0195937006024185</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6958.035</t>
+          <t>0.0133053958446252</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6903.131</t>
+          <t>0.0156247310148504</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6900.226</t>
+          <t>0.0171332513347472</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7049.658</t>
+          <t>0.0199367728433169</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>7086.909</t>
+          <t>0.0199199713540407</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7196.366</t>
+          <t>0.0199328828946529</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>7332.79</t>
+          <t>0.020869943253171</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>7720.728</t>
+          <t>0.0148154969255332</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>7618.891</t>
+          <t>0.00752873550948811</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>145787.436978897</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>141086.82183962</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>127201.43659137</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>129745.94339465</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>130798.806343329</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>118625.892780869</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>121459.216405026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>133173.760639047</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>162243.029399309</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>183289.402962845</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>189538.754053939</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>200242.206394935</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>229984.011665091</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>260066.435398422</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>249276.082989467</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>11023.737</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11375.771</t>
+          <t>166925.935825279</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10945.338</t>
+          <t>150238.850509246</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11223.996</t>
+          <t>152780.082432811</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>12536.142</t>
+          <t>153789.385768597</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>13446.884</t>
+          <t>139092.734411134</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>14625.027</t>
+          <t>142257.524134406</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15977.365</t>
+          <t>155622.068038809</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19530.036</t>
+          <t>189850.98373018</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>20891.766</t>
+          <t>214418.395190387</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20799.357</t>
+          <t>221372.722061265</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>20797.974</t>
+          <t>233856.294647683</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>20308.887</t>
+          <t>268463.02295684</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>18972.37</t>
+          <t>304290.862609071</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>19903.212</t>
+          <t>291661.720887746</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>856723.160922217</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>843663.633211832</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>758561.906929261</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>779376.667471995</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>783058.218019589</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>715560.663943996</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>718025.400210937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-15.3</t>
+          <t>774142.33641661</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-30.36</t>
+          <t>959426.798719664</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-32.59</t>
+          <t>1117434.49111651</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-30.94</t>
+          <t>1178579.94687948</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-29.36</t>
+          <t>1273352.67021226</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>1476781.63982967</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>1691948.83062529</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-20.5</t>
+          <t>1618600.58645843</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>174972.110251644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>180485.867200163</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.903</t>
+          <t>183477.087066379</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.031</t>
+          <t>192019.397675357</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>197541.591392764</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>204298.36309091</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.146</t>
+          <t>205733.840799611</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.936</t>
+          <t>203974.716814737</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>204434.566816834</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>206651.714656127</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.672</t>
+          <t>211469.592023376</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>218010.089434338</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>225203.004860929</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>222432.517407521</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>145787.436978897</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>148108.679842194</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>153161.249872419</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>156268.66213584</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>164173.134836257</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>169757.696272514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>176199.126719409</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>177163.450461632</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>175487.571196141</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>176234.781917319</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>177815.765467754</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>181904.498785449</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>187670.198415123</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>193154.220820428</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>190343.137159385</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>83827.3371474317</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80070.467084721</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>73070.4469907535</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75720.8192271894</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>72656.0149914032</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>68224.621108866</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>65694.5345055935</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>71096.0202611915</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>89452.1209498204</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107950.963989613</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>114334.715688735</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>121832.704612317</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140566.39357316</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>149211.500500929</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>131472.882622254</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>11309589249.3109</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>11480778148.1867</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11789315221.3805</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>12150817046.8161</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>12489084399.9549</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>13113577672.1064</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>13477286997.7591</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13533132948.707</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>13601571389.2713</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>14083632715.3079</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>14363250211.5462</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>14691554428.7859</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>15033817207.7353</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>15924993498.8975</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>15822846161.5346</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>13637054501.4147</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>13879477982.2342</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>14258067119.5708</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>14647150669.1955</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>15045754772.4849</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>15740278418.849</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16146021096.6998</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>16192208313.4864</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>16320430443.5021</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>16906051819.7242</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17232558974.4055</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>17644971338.0964</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>18012981864.2733</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>19049861102.2779</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>19064151101.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6320031462.34318</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6341727085.4783</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6438945495.18405</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6534907301.43032</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6624338155.01936</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6854747498.66849</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6958035095.64287</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>6903131078.49035</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6900225791.5892</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>7049658274.60795</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>7086909210.74418</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>7196366486.35599</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7332789538.14424</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>7720727852.61228</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>7618890997.6191</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3867180</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3877602</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3904154</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3972758</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4027605</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4108957</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4165431</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4158946</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4160432</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4198741</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4258009</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4308495</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4378108</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4449893.32227832</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4437555.55062773</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3168922</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3173179</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3198472</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3267797</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3322574</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3407095</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3469614</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3469893</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3471630</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3507058</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3563414</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3609450</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3672415</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3738337</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3716888</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5537161563.7762</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5534510709.31955</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5603696769.77835</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5685501816.20563</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5787519958.512</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5961599139.40131</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6030447322.11266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5990894959.81838</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5992714488.46031</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6057565469.25483</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6122792221.14095</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6209157272.36833</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6331201978.02203</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6412833763.09854</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6293109306.44956</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4595100000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4585600000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4644600000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4729200000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4818400000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4982100000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5057800000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5033100000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5028400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5082200000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5.144e+09</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5218200000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5322600000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5400100000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5284400000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.165843288808873</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16971428572366</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.172865910570744</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.175109402495878</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.177047456686726</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.178402507200353</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.179995020415257</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.180132552108903</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.166563098005101</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.191720799927915</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.195351821530963</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.198012537488662</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.203713298460781</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.223534403901085</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.225223664202211</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.445526173294926</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.457877195974051</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.467406095339612</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.475852796445434</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.480561974817937</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.49979139344762</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.511218651781974</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.519639347364957</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.502523407533596</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.545194857547996</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.554528964233844</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.561598394579096</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.573414145424168</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.564980568882856</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.569376291647569</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.388630537896201</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.372408518302289</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.359727994089643</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.349037801058688</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.342390568495337</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.321806099352027</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.308786327802769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.30022810052614</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.330913494461304</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.263084342524089</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.250119214235193</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.240389067932242</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.222872556115051</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.21148502721606</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.20540004415022</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.295356757269898</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.300043830085986</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.30387931680274</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.306243799212082</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.3076386966893</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.307638918727479</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.309575133915821</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.31115236386445</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.31149309581594</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.32095699670793</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.32249585075525</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.322806633897985</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.332069674114175</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.367327769700386</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.367746217778343</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.505332216895786</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.512543164284425</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.517893931658126</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.522917794145958</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.527121105523797</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.537838422668512</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.54431071529447</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.548614893014351</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.553043006109559</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.559063799365315</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.564314313288735</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.569055971618182</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.566531760403428</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.540852224446333</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.543359516129222</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.199311025834316</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.187413005629588</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.178226751539135</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.17083840664196</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.165240197786903</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.154522658604009</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.146114150789709</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.1402327431212</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.135463898074501</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.119979203926755</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.113189835956015</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.108137394483833</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.101398565482396</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0918200058532812</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0888942660924353</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>565662.49026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>551434.48693</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>507003.8431</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>522685.70802</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>523220.59463</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>492505.09565</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>496622.57662</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>526176.36293</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>637060.47889</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>745492.87068</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>783492.97772</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>848835.80683</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>978761.05105</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1103399.79032</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>972907.41524</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>256265.39088</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>246996.40291</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>223309.2975</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>228500.90166</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226445.40076</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>207317.35552</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>207952.05864</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>226718.0883</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>279303.10468</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>322369.35918</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>335707.43775</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>355688.99926</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>409029.41653</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>453502.36311</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>423134.60351</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>625363.65605692</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>642240.787117299</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>660940.924905751</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>680429.847094052</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>700182.100497513</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>721449.55282383</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>742284.419267126</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>759731.713392547</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>776340.031278286</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>796201.566599279</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>818671.25242229</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>841202.487809592</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>866528.736035931</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>892642.539159863</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>914298.655567405</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
